--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629809</v>
+        <v>121629807</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432828</v>
+        <v>432890</v>
       </c>
       <c r="R2" t="n">
-        <v>6838396</v>
+        <v>6838363</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629806</v>
+        <v>121629805</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,27 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432906</v>
+        <v>432828</v>
       </c>
       <c r="R3" t="n">
-        <v>6838366</v>
+        <v>6838396</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629807</v>
+        <v>121629802</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +903,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432890</v>
+        <v>432627</v>
       </c>
       <c r="R4" t="n">
-        <v>6838363</v>
+        <v>6837978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +975,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,7 +996,7 @@
         <v>121629804</v>
       </c>
       <c r="B5" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629802</v>
+        <v>121629806</v>
       </c>
       <c r="B6" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432627</v>
+        <v>432906</v>
       </c>
       <c r="R6" t="n">
-        <v>6837978</v>
+        <v>6838366</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629806</v>
+        <v>121629809</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,27 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432906</v>
+        <v>432828</v>
       </c>
       <c r="R4" t="n">
-        <v>6838366</v>
+        <v>6838396</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629805</v>
+        <v>121629806</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1009,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432828</v>
+        <v>432906</v>
       </c>
       <c r="R5" t="n">
-        <v>6838396</v>
+        <v>6838366</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629807</v>
+        <v>121629809</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432890</v>
+        <v>432828</v>
       </c>
       <c r="R2" t="n">
-        <v>6838363</v>
+        <v>6838396</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629804</v>
+        <v>121629802</v>
       </c>
       <c r="B3" t="n">
-        <v>78352</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432726</v>
+        <v>432627</v>
       </c>
       <c r="R3" t="n">
-        <v>6838233</v>
+        <v>6837978</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +869,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629809</v>
+        <v>121629804</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432828</v>
+        <v>432726</v>
       </c>
       <c r="R4" t="n">
-        <v>6838396</v>
+        <v>6838233</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629802</v>
+        <v>121629807</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,27 +1115,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432627</v>
+        <v>432890</v>
       </c>
       <c r="R6" t="n">
-        <v>6837978</v>
+        <v>6838363</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1187,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629809</v>
+        <v>121629807</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432828</v>
+        <v>432890</v>
       </c>
       <c r="R2" t="n">
-        <v>6838396</v>
+        <v>6838363</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629804</v>
+        <v>121629805</v>
       </c>
       <c r="B4" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432726</v>
+        <v>432828</v>
       </c>
       <c r="R4" t="n">
-        <v>6838233</v>
+        <v>6838396</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629806</v>
+        <v>121629804</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>78352</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,27 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432906</v>
+        <v>432726</v>
       </c>
       <c r="R5" t="n">
-        <v>6838366</v>
+        <v>6838233</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629807</v>
+        <v>121629806</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,26 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432890</v>
+        <v>432906</v>
       </c>
       <c r="R6" t="n">
-        <v>6838363</v>
+        <v>6838366</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1186,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629807</v>
+        <v>121629805</v>
       </c>
       <c r="B2" t="n">
         <v>78616</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432890</v>
+        <v>432828</v>
       </c>
       <c r="R2" t="n">
-        <v>6838363</v>
+        <v>6838396</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629802</v>
+        <v>121629807</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,27 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432627</v>
+        <v>432890</v>
       </c>
       <c r="R3" t="n">
-        <v>6837978</v>
+        <v>6838363</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629805</v>
+        <v>121629806</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +903,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432828</v>
+        <v>432906</v>
       </c>
       <c r="R4" t="n">
-        <v>6838396</v>
+        <v>6838366</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +975,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629804</v>
+        <v>121629802</v>
       </c>
       <c r="B5" t="n">
-        <v>78352</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1009,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432726</v>
+        <v>432627</v>
       </c>
       <c r="R5" t="n">
-        <v>6838233</v>
+        <v>6837978</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629806</v>
+        <v>121629804</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>78352</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,27 +1115,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432906</v>
+        <v>432726</v>
       </c>
       <c r="R6" t="n">
-        <v>6838366</v>
+        <v>6838233</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1187,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629805</v>
+        <v>121629804</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>78352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432828</v>
+        <v>432726</v>
       </c>
       <c r="R2" t="n">
-        <v>6838396</v>
+        <v>6838233</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629807</v>
+        <v>121629802</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432890</v>
+        <v>432627</v>
       </c>
       <c r="R3" t="n">
-        <v>6838363</v>
+        <v>6837978</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +869,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629806</v>
+        <v>121629809</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,27 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432906</v>
+        <v>432828</v>
       </c>
       <c r="R4" t="n">
-        <v>6838366</v>
+        <v>6838396</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629802</v>
+        <v>121629807</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,27 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432627</v>
+        <v>432890</v>
       </c>
       <c r="R5" t="n">
-        <v>6837978</v>
+        <v>6838363</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629804</v>
+        <v>121629806</v>
       </c>
       <c r="B6" t="n">
-        <v>78352</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,26 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432726</v>
+        <v>432906</v>
       </c>
       <c r="R6" t="n">
-        <v>6838233</v>
+        <v>6838366</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1186,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629804</v>
+        <v>121629807</v>
       </c>
       <c r="B2" t="n">
-        <v>78352</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432726</v>
+        <v>432890</v>
       </c>
       <c r="R2" t="n">
-        <v>6838233</v>
+        <v>6838363</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629802</v>
+        <v>121629804</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>78352</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,27 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432627</v>
+        <v>432726</v>
       </c>
       <c r="R3" t="n">
-        <v>6837978</v>
+        <v>6838233</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629809</v>
+        <v>121629806</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +903,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432828</v>
+        <v>432906</v>
       </c>
       <c r="R4" t="n">
-        <v>6838396</v>
+        <v>6838366</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +975,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629807</v>
+        <v>121629805</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432890</v>
+        <v>432828</v>
       </c>
       <c r="R5" t="n">
-        <v>6838363</v>
+        <v>6838396</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629806</v>
+        <v>121629802</v>
       </c>
       <c r="B6" t="n">
         <v>57510</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432906</v>
+        <v>432627</v>
       </c>
       <c r="R6" t="n">
-        <v>6838366</v>
+        <v>6837978</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629807</v>
+        <v>121629802</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>57518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432890</v>
+        <v>432627</v>
       </c>
       <c r="R2" t="n">
-        <v>6838363</v>
+        <v>6837978</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629804</v>
+        <v>121629807</v>
       </c>
       <c r="B3" t="n">
-        <v>78352</v>
+        <v>78629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432726</v>
+        <v>432890</v>
       </c>
       <c r="R3" t="n">
-        <v>6838233</v>
+        <v>6838363</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629806</v>
+        <v>121629805</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>78629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,27 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432906</v>
+        <v>432828</v>
       </c>
       <c r="R4" t="n">
-        <v>6838366</v>
+        <v>6838396</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629805</v>
+        <v>121629806</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1009,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432828</v>
+        <v>432906</v>
       </c>
       <c r="R5" t="n">
-        <v>6838396</v>
+        <v>6838366</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1080,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629802</v>
+        <v>121629804</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>78365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,27 +1115,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1143,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432627</v>
+        <v>432726</v>
       </c>
       <c r="R6" t="n">
-        <v>6837978</v>
+        <v>6838233</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1187,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629805</v>
+        <v>121629806</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +903,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432828</v>
+        <v>432906</v>
       </c>
       <c r="R4" t="n">
-        <v>6838396</v>
+        <v>6838366</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +975,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629806</v>
+        <v>121629805</v>
       </c>
       <c r="B5" t="n">
-        <v>57518</v>
+        <v>78629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,27 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432906</v>
+        <v>432828</v>
       </c>
       <c r="R5" t="n">
-        <v>6838366</v>
+        <v>6838396</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629802</v>
+        <v>121629804</v>
       </c>
       <c r="B2" t="n">
-        <v>57518</v>
+        <v>78367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432627</v>
+        <v>432726</v>
       </c>
       <c r="R2" t="n">
-        <v>6837978</v>
+        <v>6838233</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629807</v>
+        <v>121629805</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432890</v>
+        <v>432828</v>
       </c>
       <c r="R3" t="n">
-        <v>6838363</v>
+        <v>6838396</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629806</v>
+        <v>121629802</v>
       </c>
       <c r="B4" t="n">
         <v>57518</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432906</v>
+        <v>432627</v>
       </c>
       <c r="R4" t="n">
-        <v>6838366</v>
+        <v>6837978</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629805</v>
+        <v>121629807</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432828</v>
+        <v>432890</v>
       </c>
       <c r="R5" t="n">
-        <v>6838396</v>
+        <v>6838363</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629804</v>
+        <v>121629806</v>
       </c>
       <c r="B6" t="n">
-        <v>78365</v>
+        <v>57518</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,26 +1115,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432726</v>
+        <v>432906</v>
       </c>
       <c r="R6" t="n">
-        <v>6838233</v>
+        <v>6838366</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1186,7 +1187,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121629804</v>
+        <v>121629805</v>
       </c>
       <c r="B2" t="n">
-        <v>78367</v>
+        <v>78632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432726</v>
+        <v>432828</v>
       </c>
       <c r="R2" t="n">
-        <v>6838233</v>
+        <v>6838396</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629805</v>
+        <v>121629802</v>
       </c>
       <c r="B3" t="n">
-        <v>78631</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432828</v>
+        <v>432627</v>
       </c>
       <c r="R3" t="n">
-        <v>6838396</v>
+        <v>6837978</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,7 +869,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629802</v>
+        <v>121629807</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>78632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,27 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432627</v>
+        <v>432890</v>
       </c>
       <c r="R4" t="n">
-        <v>6837978</v>
+        <v>6838363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,6 +974,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121629807</v>
+        <v>121629804</v>
       </c>
       <c r="B5" t="n">
-        <v>78631</v>
+        <v>78368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432890</v>
+        <v>432726</v>
       </c>
       <c r="R5" t="n">
-        <v>6838363</v>
+        <v>6838233</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>121629805</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -781,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121629802</v>
+        <v>121629807</v>
       </c>
       <c r="B3" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432627</v>
+        <v>432890</v>
       </c>
       <c r="R3" t="n">
-        <v>6837978</v>
+        <v>6838363</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121629807</v>
+        <v>121629803</v>
       </c>
       <c r="B4" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432890</v>
+        <v>432597</v>
       </c>
       <c r="R4" t="n">
-        <v>6838363</v>
+        <v>6837981</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,12 +981,7 @@
         <v>121629804</v>
       </c>
       <c r="B5" t="n">
-        <v>78368</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121629806</v>
+        <v>121629802</v>
       </c>
       <c r="B6" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432906</v>
+        <v>432627</v>
       </c>
       <c r="R6" t="n">
-        <v>6838366</v>
+        <v>6837978</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,6 +1177,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121629806</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åkvandaren, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>432906</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6838366</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54545-2024 artfynd.xlsx
+++ b/artfynd/A 54545-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121629805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121629807</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121629803</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121629804</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121629802</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121629806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>